--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>100560090</t>
+          <t>100560100</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>100560090</t>
+          <t>100560100</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -620,7 +620,7 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>100560090</t>
+          <t>100560100</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -737,7 +737,7 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>76553</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="D9" s="0" t="n"/>
@@ -854,7 +854,7 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>70283</t>
+          <t>70276</t>
         </is>
       </c>
       <c r="D10" s="0" t="n"/>
@@ -893,7 +893,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>70276</t>
+          <t>70776</t>
         </is>
       </c>
       <c r="D11" s="0" t="n"/>
@@ -932,7 +932,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>70776</t>
+          <t>72332</t>
         </is>
       </c>
       <c r="D12" s="0" t="n"/>
@@ -971,7 +971,7 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>76862</t>
+          <t>72362</t>
         </is>
       </c>
       <c r="D13" s="0" t="n"/>
@@ -1010,7 +1010,7 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>76988</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="D14" s="0" t="n"/>
@@ -1049,7 +1049,7 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>72332</t>
+          <t>72333</t>
         </is>
       </c>
       <c r="D15" s="0" t="n"/>
@@ -1088,7 +1088,7 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>76385</t>
         </is>
       </c>
       <c r="D16" s="0" t="n"/>
@@ -1127,7 +1127,7 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>38613</t>
         </is>
       </c>
       <c r="D17" s="0" t="n"/>
@@ -1166,7 +1166,7 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="D18" s="0" t="n"/>
@@ -1205,7 +1205,7 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>76385</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="D19" s="0" t="n"/>
@@ -1244,7 +1244,7 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>70706</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="D20" s="0" t="n"/>
@@ -1283,7 +1283,7 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="D21" s="0" t="n"/>
@@ -1322,7 +1322,7 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="D22" s="0" t="n"/>
@@ -1361,7 +1361,7 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>76008</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="D23" s="0" t="n"/>
@@ -1400,7 +1400,7 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>76514</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="D24" s="0" t="n"/>
@@ -1439,7 +1439,7 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>43714</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="D25" s="0" t="n"/>
@@ -1478,7 +1478,7 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>100560091</t>
+          <t>100560101</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>70284</t>
+          <t>38493</t>
         </is>
       </c>
       <c r="D26" s="0" t="n"/>
@@ -1517,7 +1517,7 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>70332</t>
+          <t>70706</t>
         </is>
       </c>
       <c r="D27" s="0" t="n"/>
@@ -1556,7 +1556,7 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>76025</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="D28" s="0" t="n"/>
@@ -1595,7 +1595,7 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>76224</t>
+          <t>76008</t>
         </is>
       </c>
       <c r="D29" s="0" t="n"/>
@@ -1634,7 +1634,7 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>76493</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="D30" s="0" t="n"/>
@@ -1673,7 +1673,7 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>81814</t>
+          <t>70284</t>
         </is>
       </c>
       <c r="D31" s="0" t="n"/>
@@ -1712,7 +1712,7 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>76453</t>
+          <t>70332</t>
         </is>
       </c>
       <c r="D32" s="0" t="n"/>
@@ -1751,7 +1751,7 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>76808</t>
+          <t>76025</t>
         </is>
       </c>
       <c r="D33" s="0" t="n"/>
@@ -1790,7 +1790,7 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>76302</t>
+          <t>76224</t>
         </is>
       </c>
       <c r="D34" s="0" t="n"/>
@@ -1829,7 +1829,7 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>100560092</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>76940</t>
+          <t>76493</t>
         </is>
       </c>
       <c r="D35" s="0" t="n"/>
@@ -1868,17 +1868,17 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>100560093</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>76453</t>
         </is>
       </c>
       <c r="D36" s="0" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
@@ -1907,17 +1907,17 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>100560093</t>
+          <t>100560102</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>76493</t>
+          <t>76302</t>
         </is>
       </c>
       <c r="D37" s="0" t="n"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
@@ -1946,17 +1946,17 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>100560093</t>
+          <t>100560103</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>76940</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="D38" s="0" t="n"/>
@@ -1985,17 +1985,17 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>100560093</t>
+          <t>100560103</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>81814</t>
+          <t>76493</t>
         </is>
       </c>
       <c r="D39" s="0" t="n"/>
@@ -2024,7 +2024,7 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>100560094</t>
+          <t>100560104</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>100560094</t>
+          <t>100560105</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>76899</t>
+          <t>76008</t>
         </is>
       </c>
       <c r="D41" s="0" t="n"/>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="G41" s="0" t="inlineStr">
@@ -2102,7 +2102,7 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>100560095</t>
+          <t>100560106</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>72333</t>
         </is>
       </c>
       <c r="D42" s="0" t="n"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>100560095</t>
+          <t>100560106</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>76008</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="D43" s="0" t="n"/>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G43" s="0" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>100560095</t>
+          <t>100560106</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>81814</t>
+          <t>72332</t>
         </is>
       </c>
       <c r="D44" s="0" t="n"/>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
@@ -2219,17 +2219,17 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>100560096</t>
+          <t>100560106</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>72362</t>
         </is>
       </c>
       <c r="D45" s="0" t="n"/>
@@ -2258,17 +2258,17 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>100560096</t>
+          <t>100560107</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>70973</t>
         </is>
       </c>
       <c r="D46" s="0" t="n"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="G46" s="0" t="inlineStr">
@@ -2297,17 +2297,17 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>100560096</t>
+          <t>100560108</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>72332</t>
+          <t>70973</t>
         </is>
       </c>
       <c r="D47" s="0" t="n"/>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="G47" s="0" t="inlineStr">
@@ -2334,160 +2334,48 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="inlineStr">
-        <is>
-          <t>100560096</t>
-        </is>
-      </c>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>72362</t>
-        </is>
-      </c>
+      <c r="A48" s="0" t="n"/>
+      <c r="B48" s="0" t="n"/>
+      <c r="C48" s="0" t="n"/>
       <c r="D48" s="0" t="n"/>
-      <c r="E48" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>4004</t>
-        </is>
-      </c>
-      <c r="G48" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E48" s="0" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="0" t="n"/>
       <c r="H48" s="0" t="n"/>
-      <c r="I48" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I48" s="0" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="inlineStr">
-        <is>
-          <t>100560097</t>
-        </is>
-      </c>
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="0" t="inlineStr">
-        <is>
-          <t>81814</t>
-        </is>
-      </c>
+      <c r="A49" s="0" t="n"/>
+      <c r="B49" s="0" t="n"/>
+      <c r="C49" s="0" t="n"/>
       <c r="D49" s="0" t="n"/>
-      <c r="E49" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>4901</t>
-        </is>
-      </c>
-      <c r="G49" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E49" s="0" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="0" t="n"/>
       <c r="H49" s="0" t="n"/>
-      <c r="I49" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I49" s="0" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="0" t="inlineStr">
-        <is>
-          <t>100560098</t>
-        </is>
-      </c>
-      <c r="B50" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>70973</t>
-        </is>
-      </c>
+      <c r="A50" s="0" t="n"/>
+      <c r="B50" s="0" t="n"/>
+      <c r="C50" s="0" t="n"/>
       <c r="D50" s="0" t="n"/>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>9001</t>
-        </is>
-      </c>
-      <c r="G50" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E50" s="0" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="0" t="n"/>
       <c r="H50" s="0" t="n"/>
-      <c r="I50" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I50" s="0" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="0" t="inlineStr">
-        <is>
-          <t>100560099</t>
-        </is>
-      </c>
-      <c r="B51" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>70973</t>
-        </is>
-      </c>
+      <c r="A51" s="0" t="n"/>
+      <c r="B51" s="0" t="n"/>
+      <c r="C51" s="0" t="n"/>
       <c r="D51" s="0" t="n"/>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>9095</t>
-        </is>
-      </c>
-      <c r="G51" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E51" s="0" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="0" t="n"/>
       <c r="H51" s="0" t="n"/>
-      <c r="I51" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I51" s="0" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="0" t="n"/>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>100560100</t>
+          <t>100560109</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="D2" s="0" t="n"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>100560100</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>72332</t>
+          <t>70973</t>
         </is>
       </c>
       <c r="D3" s="0" t="n"/>
@@ -602,7 +602,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
@@ -620,17 +620,17 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>100560100</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>73377</t>
         </is>
       </c>
       <c r="D4" s="0" t="n"/>
@@ -641,7 +641,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
@@ -659,17 +659,17 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>71292</t>
         </is>
       </c>
       <c r="D5" s="0" t="n"/>
@@ -698,17 +698,17 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>70973</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="D6" s="0" t="n"/>
@@ -737,17 +737,17 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>73377</t>
+          <t>70276</t>
         </is>
       </c>
       <c r="D7" s="0" t="n"/>
@@ -776,17 +776,17 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>71292</t>
+          <t>70776</t>
         </is>
       </c>
       <c r="D8" s="0" t="n"/>
@@ -815,17 +815,17 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>70283</t>
+          <t>72332</t>
         </is>
       </c>
       <c r="D9" s="0" t="n"/>
@@ -854,17 +854,17 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>70276</t>
+          <t>72362</t>
         </is>
       </c>
       <c r="D10" s="0" t="n"/>
@@ -893,17 +893,17 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>70776</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="D11" s="0" t="n"/>
@@ -932,17 +932,17 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>72332</t>
+          <t>72333</t>
         </is>
       </c>
       <c r="D12" s="0" t="n"/>
@@ -971,17 +971,17 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>38613</t>
         </is>
       </c>
       <c r="D13" s="0" t="n"/>
@@ -1010,17 +1010,17 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="D14" s="0" t="n"/>
@@ -1049,17 +1049,17 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>72333</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="D15" s="0" t="n"/>
@@ -1088,17 +1088,17 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>76385</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="D16" s="0" t="n"/>
@@ -1127,17 +1127,17 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>38613</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="D17" s="0" t="n"/>
@@ -1166,17 +1166,17 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="D18" s="0" t="n"/>
@@ -1205,17 +1205,17 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="D19" s="0" t="n"/>
@@ -1244,17 +1244,17 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="D20" s="0" t="n"/>
@@ -1283,17 +1283,17 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>38493</t>
         </is>
       </c>
       <c r="D21" s="0" t="n"/>
@@ -1322,17 +1322,17 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>70706</t>
         </is>
       </c>
       <c r="D22" s="0" t="n"/>
@@ -1361,17 +1361,17 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="D23" s="0" t="n"/>
@@ -1400,17 +1400,17 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560110</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="D24" s="0" t="n"/>
@@ -1439,17 +1439,17 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560111</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>70284</t>
         </is>
       </c>
       <c r="D25" s="0" t="n"/>
@@ -1478,17 +1478,17 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>100560101</t>
+          <t>100560111</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>70332</t>
         </is>
       </c>
       <c r="D26" s="0" t="n"/>
@@ -1515,823 +1515,235 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B27" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>70706</t>
-        </is>
-      </c>
+      <c r="A27" s="0" t="n"/>
+      <c r="B27" s="0" t="n"/>
+      <c r="C27" s="0" t="n"/>
       <c r="D27" s="0" t="n"/>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E27" s="0" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="0" t="n"/>
       <c r="H27" s="0" t="n"/>
-      <c r="I27" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I27" s="0" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>70980</t>
-        </is>
-      </c>
+      <c r="A28" s="0" t="n"/>
+      <c r="B28" s="0" t="n"/>
+      <c r="C28" s="0" t="n"/>
       <c r="D28" s="0" t="n"/>
-      <c r="E28" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E28" s="0" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="0" t="n"/>
       <c r="H28" s="0" t="n"/>
-      <c r="I28" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I28" s="0" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>76008</t>
-        </is>
-      </c>
+      <c r="A29" s="0" t="n"/>
+      <c r="B29" s="0" t="n"/>
+      <c r="C29" s="0" t="n"/>
       <c r="D29" s="0" t="n"/>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E29" s="0" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="0" t="n"/>
       <c r="H29" s="0" t="n"/>
-      <c r="I29" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I29" s="0" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>43714</t>
-        </is>
-      </c>
+      <c r="A30" s="0" t="n"/>
+      <c r="B30" s="0" t="n"/>
+      <c r="C30" s="0" t="n"/>
       <c r="D30" s="0" t="n"/>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G30" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E30" s="0" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="0" t="n"/>
       <c r="H30" s="0" t="n"/>
-      <c r="I30" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I30" s="0" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>70284</t>
-        </is>
-      </c>
+      <c r="A31" s="0" t="n"/>
+      <c r="B31" s="0" t="n"/>
+      <c r="C31" s="0" t="n"/>
       <c r="D31" s="0" t="n"/>
-      <c r="E31" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E31" s="0" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="0" t="n"/>
       <c r="H31" s="0" t="n"/>
-      <c r="I31" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I31" s="0" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t>70332</t>
-        </is>
-      </c>
+      <c r="A32" s="0" t="n"/>
+      <c r="B32" s="0" t="n"/>
+      <c r="C32" s="0" t="n"/>
       <c r="D32" s="0" t="n"/>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E32" s="0" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="0" t="n"/>
       <c r="H32" s="0" t="n"/>
-      <c r="I32" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I32" s="0" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t>76025</t>
-        </is>
-      </c>
+      <c r="A33" s="0" t="n"/>
+      <c r="B33" s="0" t="n"/>
+      <c r="C33" s="0" t="n"/>
       <c r="D33" s="0" t="n"/>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E33" s="0" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="0" t="n"/>
       <c r="H33" s="0" t="n"/>
-      <c r="I33" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I33" s="0" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>76224</t>
-        </is>
-      </c>
+      <c r="A34" s="0" t="n"/>
+      <c r="B34" s="0" t="n"/>
+      <c r="C34" s="0" t="n"/>
       <c r="D34" s="0" t="n"/>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E34" s="0" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="0" t="n"/>
       <c r="H34" s="0" t="n"/>
-      <c r="I34" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I34" s="0" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>76493</t>
-        </is>
-      </c>
+      <c r="A35" s="0" t="n"/>
+      <c r="B35" s="0" t="n"/>
+      <c r="C35" s="0" t="n"/>
       <c r="D35" s="0" t="n"/>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E35" s="0" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="0" t="n"/>
       <c r="H35" s="0" t="n"/>
-      <c r="I35" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I35" s="0" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>76453</t>
-        </is>
-      </c>
+      <c r="A36" s="0" t="n"/>
+      <c r="B36" s="0" t="n"/>
+      <c r="C36" s="0" t="n"/>
       <c r="D36" s="0" t="n"/>
-      <c r="E36" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E36" s="0" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="0" t="n"/>
       <c r="H36" s="0" t="n"/>
-      <c r="I36" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I36" s="0" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="inlineStr">
-        <is>
-          <t>100560102</t>
-        </is>
-      </c>
-      <c r="B37" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t>76302</t>
-        </is>
-      </c>
+      <c r="A37" s="0" t="n"/>
+      <c r="B37" s="0" t="n"/>
+      <c r="C37" s="0" t="n"/>
       <c r="D37" s="0" t="n"/>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G37" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E37" s="0" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="0" t="n"/>
       <c r="H37" s="0" t="n"/>
-      <c r="I37" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I37" s="0" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="inlineStr">
-        <is>
-          <t>100560103</t>
-        </is>
-      </c>
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>70980</t>
-        </is>
-      </c>
+      <c r="A38" s="0" t="n"/>
+      <c r="B38" s="0" t="n"/>
+      <c r="C38" s="0" t="n"/>
       <c r="D38" s="0" t="n"/>
-      <c r="E38" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E38" s="0" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="0" t="n"/>
       <c r="H38" s="0" t="n"/>
-      <c r="I38" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I38" s="0" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="inlineStr">
-        <is>
-          <t>100560103</t>
-        </is>
-      </c>
-      <c r="B39" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>76493</t>
-        </is>
-      </c>
+      <c r="A39" s="0" t="n"/>
+      <c r="B39" s="0" t="n"/>
+      <c r="C39" s="0" t="n"/>
       <c r="D39" s="0" t="n"/>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="G39" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E39" s="0" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="0" t="n"/>
       <c r="H39" s="0" t="n"/>
-      <c r="I39" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I39" s="0" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="inlineStr">
-        <is>
-          <t>100560104</t>
-        </is>
-      </c>
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>76008</t>
-        </is>
-      </c>
+      <c r="A40" s="0" t="n"/>
+      <c r="B40" s="0" t="n"/>
+      <c r="C40" s="0" t="n"/>
       <c r="D40" s="0" t="n"/>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="G40" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E40" s="0" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="0" t="n"/>
       <c r="H40" s="0" t="n"/>
-      <c r="I40" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I40" s="0" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="inlineStr">
-        <is>
-          <t>100560105</t>
-        </is>
-      </c>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>76008</t>
-        </is>
-      </c>
+      <c r="A41" s="0" t="n"/>
+      <c r="B41" s="0" t="n"/>
+      <c r="C41" s="0" t="n"/>
       <c r="D41" s="0" t="n"/>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="G41" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E41" s="0" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="0" t="n"/>
       <c r="H41" s="0" t="n"/>
-      <c r="I41" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I41" s="0" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="inlineStr">
-        <is>
-          <t>100560106</t>
-        </is>
-      </c>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>72333</t>
-        </is>
-      </c>
+      <c r="A42" s="0" t="n"/>
+      <c r="B42" s="0" t="n"/>
+      <c r="C42" s="0" t="n"/>
       <c r="D42" s="0" t="n"/>
-      <c r="E42" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>4004</t>
-        </is>
-      </c>
-      <c r="G42" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E42" s="0" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="0" t="n"/>
       <c r="H42" s="0" t="n"/>
-      <c r="I42" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I42" s="0" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="inlineStr">
-        <is>
-          <t>100560106</t>
-        </is>
-      </c>
-      <c r="B43" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t>71395</t>
-        </is>
-      </c>
+      <c r="A43" s="0" t="n"/>
+      <c r="B43" s="0" t="n"/>
+      <c r="C43" s="0" t="n"/>
       <c r="D43" s="0" t="n"/>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>4004</t>
-        </is>
-      </c>
-      <c r="G43" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E43" s="0" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="0" t="n"/>
       <c r="H43" s="0" t="n"/>
-      <c r="I43" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I43" s="0" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="0" t="inlineStr">
-        <is>
-          <t>100560106</t>
-        </is>
-      </c>
-      <c r="B44" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t>72332</t>
-        </is>
-      </c>
+      <c r="A44" s="0" t="n"/>
+      <c r="B44" s="0" t="n"/>
+      <c r="C44" s="0" t="n"/>
       <c r="D44" s="0" t="n"/>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>4004</t>
-        </is>
-      </c>
-      <c r="G44" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E44" s="0" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="0" t="n"/>
       <c r="H44" s="0" t="n"/>
-      <c r="I44" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I44" s="0" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="0" t="inlineStr">
-        <is>
-          <t>100560106</t>
-        </is>
-      </c>
-      <c r="B45" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>72362</t>
-        </is>
-      </c>
+      <c r="A45" s="0" t="n"/>
+      <c r="B45" s="0" t="n"/>
+      <c r="C45" s="0" t="n"/>
       <c r="D45" s="0" t="n"/>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>4004</t>
-        </is>
-      </c>
-      <c r="G45" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E45" s="0" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="0" t="n"/>
       <c r="H45" s="0" t="n"/>
-      <c r="I45" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I45" s="0" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="0" t="inlineStr">
-        <is>
-          <t>100560107</t>
-        </is>
-      </c>
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>70973</t>
-        </is>
-      </c>
+      <c r="A46" s="0" t="n"/>
+      <c r="B46" s="0" t="n"/>
+      <c r="C46" s="0" t="n"/>
       <c r="D46" s="0" t="n"/>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>9001</t>
-        </is>
-      </c>
-      <c r="G46" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E46" s="0" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="0" t="n"/>
       <c r="H46" s="0" t="n"/>
-      <c r="I46" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I46" s="0" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="inlineStr">
-        <is>
-          <t>100560108</t>
-        </is>
-      </c>
-      <c r="B47" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>70973</t>
-        </is>
-      </c>
+      <c r="A47" s="0" t="n"/>
+      <c r="B47" s="0" t="n"/>
+      <c r="C47" s="0" t="n"/>
       <c r="D47" s="0" t="n"/>
-      <c r="E47" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>9095</t>
-        </is>
-      </c>
-      <c r="G47" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E47" s="0" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="0" t="n"/>
       <c r="H47" s="0" t="n"/>
-      <c r="I47" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I47" s="0" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="0" t="n"/>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>100560109</t>
+          <t>100585659</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="D2" s="0" t="n"/>
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>100560110</t>
+          <t>100585690</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>70973</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="D3" s="0" t="n"/>
@@ -602,7 +602,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
@@ -618,901 +618,257 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
+      <c r="A4" s="0" t="n"/>
+      <c r="B4" s="0" t="n"/>
+      <c r="C4" s="0" t="n"/>
       <c r="D4" s="0" t="n"/>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E4" s="0" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="0" t="n"/>
       <c r="H4" s="0" t="n"/>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I4" s="0" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>71292</t>
-        </is>
-      </c>
+      <c r="A5" s="0" t="n"/>
+      <c r="B5" s="0" t="n"/>
+      <c r="C5" s="0" t="n"/>
       <c r="D5" s="0" t="n"/>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E5" s="0" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="0" t="n"/>
       <c r="H5" s="0" t="n"/>
-      <c r="I5" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I5" s="0" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>70283</t>
-        </is>
-      </c>
+      <c r="A6" s="0" t="n"/>
+      <c r="B6" s="0" t="n"/>
+      <c r="C6" s="0" t="n"/>
       <c r="D6" s="0" t="n"/>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E6" s="0" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="0" t="n"/>
       <c r="H6" s="0" t="n"/>
-      <c r="I6" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I6" s="0" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>70276</t>
-        </is>
-      </c>
+      <c r="A7" s="0" t="n"/>
+      <c r="B7" s="0" t="n"/>
+      <c r="C7" s="0" t="n"/>
       <c r="D7" s="0" t="n"/>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E7" s="0" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="0" t="n"/>
       <c r="H7" s="0" t="n"/>
-      <c r="I7" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I7" s="0" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>70776</t>
-        </is>
-      </c>
+      <c r="A8" s="0" t="n"/>
+      <c r="B8" s="0" t="n"/>
+      <c r="C8" s="0" t="n"/>
       <c r="D8" s="0" t="n"/>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E8" s="0" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="0" t="n"/>
       <c r="H8" s="0" t="n"/>
-      <c r="I8" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I8" s="0" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>72332</t>
-        </is>
-      </c>
+      <c r="A9" s="0" t="n"/>
+      <c r="B9" s="0" t="n"/>
+      <c r="C9" s="0" t="n"/>
       <c r="D9" s="0" t="n"/>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E9" s="0" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="0" t="n"/>
       <c r="H9" s="0" t="n"/>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I9" s="0" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>72362</t>
-        </is>
-      </c>
+      <c r="A10" s="0" t="n"/>
+      <c r="B10" s="0" t="n"/>
+      <c r="C10" s="0" t="n"/>
       <c r="D10" s="0" t="n"/>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E10" s="0" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="0" t="n"/>
       <c r="H10" s="0" t="n"/>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I10" s="0" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>71395</t>
-        </is>
-      </c>
+      <c r="A11" s="0" t="n"/>
+      <c r="B11" s="0" t="n"/>
+      <c r="C11" s="0" t="n"/>
       <c r="D11" s="0" t="n"/>
-      <c r="E11" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E11" s="0" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="0" t="n"/>
       <c r="H11" s="0" t="n"/>
-      <c r="I11" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I11" s="0" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>72333</t>
-        </is>
-      </c>
+      <c r="A12" s="0" t="n"/>
+      <c r="B12" s="0" t="n"/>
+      <c r="C12" s="0" t="n"/>
       <c r="D12" s="0" t="n"/>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E12" s="0" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="0" t="n"/>
       <c r="H12" s="0" t="n"/>
-      <c r="I12" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I12" s="0" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>38613</t>
-        </is>
-      </c>
+      <c r="A13" s="0" t="n"/>
+      <c r="B13" s="0" t="n"/>
+      <c r="C13" s="0" t="n"/>
       <c r="D13" s="0" t="n"/>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E13" s="0" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="0" t="n"/>
       <c r="H13" s="0" t="n"/>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I13" s="0" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>38461</t>
-        </is>
-      </c>
+      <c r="A14" s="0" t="n"/>
+      <c r="B14" s="0" t="n"/>
+      <c r="C14" s="0" t="n"/>
       <c r="D14" s="0" t="n"/>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E14" s="0" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="0" t="n"/>
       <c r="H14" s="0" t="n"/>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I14" s="0" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t>38490</t>
-        </is>
-      </c>
+      <c r="A15" s="0" t="n"/>
+      <c r="B15" s="0" t="n"/>
+      <c r="C15" s="0" t="n"/>
       <c r="D15" s="0" t="n"/>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E15" s="0" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="0" t="n"/>
       <c r="H15" s="0" t="n"/>
-      <c r="I15" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I15" s="0" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
-        <is>
-          <t>38458</t>
-        </is>
-      </c>
+      <c r="A16" s="0" t="n"/>
+      <c r="B16" s="0" t="n"/>
+      <c r="C16" s="0" t="n"/>
       <c r="D16" s="0" t="n"/>
-      <c r="E16" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E16" s="0" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="0" t="n"/>
       <c r="H16" s="0" t="n"/>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I16" s="0" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>38455</t>
-        </is>
-      </c>
+      <c r="A17" s="0" t="n"/>
+      <c r="B17" s="0" t="n"/>
+      <c r="C17" s="0" t="n"/>
       <c r="D17" s="0" t="n"/>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E17" s="0" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="0" t="n"/>
       <c r="H17" s="0" t="n"/>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I17" s="0" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>38466</t>
-        </is>
-      </c>
+      <c r="A18" s="0" t="n"/>
+      <c r="B18" s="0" t="n"/>
+      <c r="C18" s="0" t="n"/>
       <c r="D18" s="0" t="n"/>
-      <c r="E18" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E18" s="0" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="0" t="n"/>
       <c r="H18" s="0" t="n"/>
-      <c r="I18" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I18" s="0" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t>38468</t>
-        </is>
-      </c>
+      <c r="A19" s="0" t="n"/>
+      <c r="B19" s="0" t="n"/>
+      <c r="C19" s="0" t="n"/>
       <c r="D19" s="0" t="n"/>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E19" s="0" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="0" t="n"/>
       <c r="H19" s="0" t="n"/>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I19" s="0" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t>38470</t>
-        </is>
-      </c>
+      <c r="A20" s="0" t="n"/>
+      <c r="B20" s="0" t="n"/>
+      <c r="C20" s="0" t="n"/>
       <c r="D20" s="0" t="n"/>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E20" s="0" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="0" t="n"/>
       <c r="H20" s="0" t="n"/>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I20" s="0" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>38493</t>
-        </is>
-      </c>
+      <c r="A21" s="0" t="n"/>
+      <c r="B21" s="0" t="n"/>
+      <c r="C21" s="0" t="n"/>
       <c r="D21" s="0" t="n"/>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E21" s="0" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="0" t="n"/>
       <c r="H21" s="0" t="n"/>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I21" s="0" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>70706</t>
-        </is>
-      </c>
+      <c r="A22" s="0" t="n"/>
+      <c r="B22" s="0" t="n"/>
+      <c r="C22" s="0" t="n"/>
       <c r="D22" s="0" t="n"/>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E22" s="0" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="0" t="n"/>
       <c r="H22" s="0" t="n"/>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I22" s="0" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>70980</t>
-        </is>
-      </c>
+      <c r="A23" s="0" t="n"/>
+      <c r="B23" s="0" t="n"/>
+      <c r="C23" s="0" t="n"/>
       <c r="D23" s="0" t="n"/>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E23" s="0" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="0" t="n"/>
       <c r="H23" s="0" t="n"/>
-      <c r="I23" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I23" s="0" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t>100560110</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>43714</t>
-        </is>
-      </c>
+      <c r="A24" s="0" t="n"/>
+      <c r="B24" s="0" t="n"/>
+      <c r="C24" s="0" t="n"/>
       <c r="D24" s="0" t="n"/>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E24" s="0" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="0" t="n"/>
       <c r="H24" s="0" t="n"/>
-      <c r="I24" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I24" s="0" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t>100560111</t>
-        </is>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>70284</t>
-        </is>
-      </c>
+      <c r="A25" s="0" t="n"/>
+      <c r="B25" s="0" t="n"/>
+      <c r="C25" s="0" t="n"/>
       <c r="D25" s="0" t="n"/>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E25" s="0" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="0" t="n"/>
       <c r="H25" s="0" t="n"/>
-      <c r="I25" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I25" s="0" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t>100560111</t>
-        </is>
-      </c>
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
-        <is>
-          <t>70332</t>
-        </is>
-      </c>
+      <c r="A26" s="0" t="n"/>
+      <c r="B26" s="0" t="n"/>
+      <c r="C26" s="0" t="n"/>
       <c r="D26" s="0" t="n"/>
-      <c r="E26" s="0" t="inlineStr">
-        <is>
-          <t>CH50</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t>Not yet counted</t>
-        </is>
-      </c>
+      <c r="E26" s="0" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="0" t="n"/>
       <c r="H26" s="0" t="n"/>
-      <c r="I26" s="0" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
+      <c r="I26" s="0" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="0" t="n"/>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>100585659</t>
+          <t>100560172</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>11106520</t>
         </is>
       </c>
       <c r="D2" s="0" t="n"/>
@@ -563,12 +563,12 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>Not yet counted</t>
+          <t>Counted, adjusted</t>
         </is>
       </c>
       <c r="H2" s="0" t="n"/>
@@ -581,17 +581,17 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>100585690</t>
+          <t>100560172</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>70283</t>
+          <t>11142113</t>
         </is>
       </c>
       <c r="D3" s="0" t="n"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Not yet counted</t>
+          <t>Counted, adjusted</t>
         </is>
       </c>
       <c r="H3" s="0" t="n"/>
@@ -618,554 +618,1932 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="n"/>
-      <c r="B4" s="0" t="n"/>
-      <c r="C4" s="0" t="n"/>
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>30134368</t>
+        </is>
+      </c>
       <c r="D4" s="0" t="n"/>
-      <c r="E4" s="0" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="0" t="n"/>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H4" s="0" t="n"/>
-      <c r="I4" s="0" t="n"/>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n"/>
-      <c r="B5" s="0" t="n"/>
-      <c r="C5" s="0" t="n"/>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>42900601</t>
+        </is>
+      </c>
       <c r="D5" s="0" t="n"/>
-      <c r="E5" s="0" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="0" t="n"/>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H5" s="0" t="n"/>
-      <c r="I5" s="0" t="n"/>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="n"/>
-      <c r="B6" s="0" t="n"/>
-      <c r="C6" s="0" t="n"/>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>42101117</t>
+        </is>
+      </c>
       <c r="D6" s="0" t="n"/>
-      <c r="E6" s="0" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="0" t="n"/>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5001</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H6" s="0" t="n"/>
-      <c r="I6" s="0" t="n"/>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="n"/>
-      <c r="B7" s="0" t="n"/>
-      <c r="C7" s="0" t="n"/>
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>42900450</t>
+        </is>
+      </c>
       <c r="D7" s="0" t="n"/>
-      <c r="E7" s="0" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="0" t="n"/>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>5001</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H7" s="0" t="n"/>
-      <c r="I7" s="0" t="n"/>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="n"/>
-      <c r="B8" s="0" t="n"/>
-      <c r="C8" s="0" t="n"/>
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>42900580</t>
+        </is>
+      </c>
       <c r="D8" s="0" t="n"/>
-      <c r="E8" s="0" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="0" t="n"/>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5002</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H8" s="0" t="n"/>
-      <c r="I8" s="0" t="n"/>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="n"/>
-      <c r="B9" s="0" t="n"/>
-      <c r="C9" s="0" t="n"/>
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>42105078</t>
+        </is>
+      </c>
       <c r="D9" s="0" t="n"/>
-      <c r="E9" s="0" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="0" t="n"/>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>5003</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H9" s="0" t="n"/>
-      <c r="I9" s="0" t="n"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="n"/>
-      <c r="B10" s="0" t="n"/>
-      <c r="C10" s="0" t="n"/>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>30089136</t>
+        </is>
+      </c>
       <c r="D10" s="0" t="n"/>
-      <c r="E10" s="0" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="0" t="n"/>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5004</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H10" s="0" t="n"/>
-      <c r="I10" s="0" t="n"/>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="n"/>
-      <c r="B11" s="0" t="n"/>
-      <c r="C11" s="0" t="n"/>
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>30675413</t>
+        </is>
+      </c>
       <c r="D11" s="0" t="n"/>
-      <c r="E11" s="0" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="0" t="n"/>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5005</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H11" s="0" t="n"/>
-      <c r="I11" s="0" t="n"/>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="n"/>
-      <c r="B12" s="0" t="n"/>
-      <c r="C12" s="0" t="n"/>
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>42101114</t>
+        </is>
+      </c>
       <c r="D12" s="0" t="n"/>
-      <c r="E12" s="0" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="0" t="n"/>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>5006</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H12" s="0" t="n"/>
-      <c r="I12" s="0" t="n"/>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="n"/>
-      <c r="B13" s="0" t="n"/>
-      <c r="C13" s="0" t="n"/>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>42105080</t>
+        </is>
+      </c>
       <c r="D13" s="0" t="n"/>
-      <c r="E13" s="0" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="0" t="n"/>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5007</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H13" s="0" t="n"/>
-      <c r="I13" s="0" t="n"/>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="n"/>
-      <c r="B14" s="0" t="n"/>
-      <c r="C14" s="0" t="n"/>
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>42911002</t>
+        </is>
+      </c>
       <c r="D14" s="0" t="n"/>
-      <c r="E14" s="0" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="0" t="n"/>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3002</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H14" s="0" t="n"/>
-      <c r="I14" s="0" t="n"/>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="n"/>
-      <c r="B15" s="0" t="n"/>
-      <c r="C15" s="0" t="n"/>
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>42900603</t>
+        </is>
+      </c>
       <c r="D15" s="0" t="n"/>
-      <c r="E15" s="0" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="0" t="n"/>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H15" s="0" t="n"/>
-      <c r="I15" s="0" t="n"/>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="n"/>
-      <c r="B16" s="0" t="n"/>
-      <c r="C16" s="0" t="n"/>
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>30311532</t>
+        </is>
+      </c>
       <c r="D16" s="0" t="n"/>
-      <c r="E16" s="0" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="0" t="n"/>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H16" s="0" t="n"/>
-      <c r="I16" s="0" t="n"/>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="n"/>
-      <c r="B17" s="0" t="n"/>
-      <c r="C17" s="0" t="n"/>
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>42700100</t>
+        </is>
+      </c>
       <c r="D17" s="0" t="n"/>
-      <c r="E17" s="0" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="0" t="n"/>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H17" s="0" t="n"/>
-      <c r="I17" s="0" t="n"/>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="n"/>
-      <c r="B18" s="0" t="n"/>
-      <c r="C18" s="0" t="n"/>
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>30372884</t>
+        </is>
+      </c>
       <c r="D18" s="0" t="n"/>
-      <c r="E18" s="0" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="0" t="n"/>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H18" s="0" t="n"/>
-      <c r="I18" s="0" t="n"/>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="n"/>
-      <c r="B19" s="0" t="n"/>
-      <c r="C19" s="0" t="n"/>
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>42910754</t>
+        </is>
+      </c>
       <c r="D19" s="0" t="n"/>
-      <c r="E19" s="0" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="0" t="n"/>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H19" s="0" t="n"/>
-      <c r="I19" s="0" t="n"/>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="n"/>
-      <c r="B20" s="0" t="n"/>
-      <c r="C20" s="0" t="n"/>
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>11138614</t>
+        </is>
+      </c>
       <c r="D20" s="0" t="n"/>
-      <c r="E20" s="0" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="0" t="n"/>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H20" s="0" t="n"/>
-      <c r="I20" s="0" t="n"/>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="n"/>
-      <c r="B21" s="0" t="n"/>
-      <c r="C21" s="0" t="n"/>
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>30515072</t>
+        </is>
+      </c>
       <c r="D21" s="0" t="n"/>
-      <c r="E21" s="0" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="0" t="n"/>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H21" s="0" t="n"/>
-      <c r="I21" s="0" t="n"/>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="n"/>
-      <c r="B22" s="0" t="n"/>
-      <c r="C22" s="0" t="n"/>
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>100560172</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>30008824</t>
+        </is>
+      </c>
       <c r="D22" s="0" t="n"/>
-      <c r="E22" s="0" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="0" t="n"/>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H22" s="0" t="n"/>
-      <c r="I22" s="0" t="n"/>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="0" t="n"/>
-      <c r="B23" s="0" t="n"/>
-      <c r="C23" s="0" t="n"/>
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>100560176</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>30300914</t>
+        </is>
+      </c>
       <c r="D23" s="0" t="n"/>
-      <c r="E23" s="0" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="0" t="n"/>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H23" s="0" t="n"/>
-      <c r="I23" s="0" t="n"/>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="n"/>
-      <c r="B24" s="0" t="n"/>
-      <c r="C24" s="0" t="n"/>
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>100560176</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>11100544</t>
+        </is>
+      </c>
       <c r="D24" s="0" t="n"/>
-      <c r="E24" s="0" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="0" t="n"/>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H24" s="0" t="n"/>
-      <c r="I24" s="0" t="n"/>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="0" t="n"/>
-      <c r="B25" s="0" t="n"/>
-      <c r="C25" s="0" t="n"/>
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>30372870</t>
+        </is>
+      </c>
       <c r="D25" s="0" t="n"/>
-      <c r="E25" s="0" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="0" t="n"/>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H25" s="0" t="n"/>
-      <c r="I25" s="0" t="n"/>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="n"/>
-      <c r="B26" s="0" t="n"/>
-      <c r="C26" s="0" t="n"/>
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>11142244</t>
+        </is>
+      </c>
       <c r="D26" s="0" t="n"/>
-      <c r="E26" s="0" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="0" t="n"/>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H26" s="0" t="n"/>
-      <c r="I26" s="0" t="n"/>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="n"/>
-      <c r="B27" s="0" t="n"/>
-      <c r="C27" s="0" t="n"/>
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>11142243</t>
+        </is>
+      </c>
       <c r="D27" s="0" t="n"/>
-      <c r="E27" s="0" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="0" t="n"/>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H27" s="0" t="n"/>
-      <c r="I27" s="0" t="n"/>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="n"/>
-      <c r="B28" s="0" t="n"/>
-      <c r="C28" s="0" t="n"/>
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>11142242</t>
+        </is>
+      </c>
       <c r="D28" s="0" t="n"/>
-      <c r="E28" s="0" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="0" t="n"/>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H28" s="0" t="n"/>
-      <c r="I28" s="0" t="n"/>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="0" t="n"/>
-      <c r="B29" s="0" t="n"/>
-      <c r="C29" s="0" t="n"/>
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>11138585</t>
+        </is>
+      </c>
       <c r="D29" s="0" t="n"/>
-      <c r="E29" s="0" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="0" t="n"/>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H29" s="0" t="n"/>
-      <c r="I29" s="0" t="n"/>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="0" t="n"/>
-      <c r="B30" s="0" t="n"/>
-      <c r="C30" s="0" t="n"/>
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>30740984</t>
+        </is>
+      </c>
       <c r="D30" s="0" t="n"/>
-      <c r="E30" s="0" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="0" t="n"/>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H30" s="0" t="n"/>
-      <c r="I30" s="0" t="n"/>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="n"/>
-      <c r="B31" s="0" t="n"/>
-      <c r="C31" s="0" t="n"/>
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>42105320</t>
+        </is>
+      </c>
       <c r="D31" s="0" t="n"/>
-      <c r="E31" s="0" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="0" t="n"/>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H31" s="0" t="n"/>
-      <c r="I31" s="0" t="n"/>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="n"/>
-      <c r="B32" s="0" t="n"/>
-      <c r="C32" s="0" t="n"/>
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>30986896</t>
+        </is>
+      </c>
       <c r="D32" s="0" t="n"/>
-      <c r="E32" s="0" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="0" t="n"/>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H32" s="0" t="n"/>
-      <c r="I32" s="0" t="n"/>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="n"/>
-      <c r="B33" s="0" t="n"/>
-      <c r="C33" s="0" t="n"/>
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>42900647</t>
+        </is>
+      </c>
       <c r="D33" s="0" t="n"/>
-      <c r="E33" s="0" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="0" t="n"/>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H33" s="0" t="n"/>
-      <c r="I33" s="0" t="n"/>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="0" t="n"/>
-      <c r="B34" s="0" t="n"/>
-      <c r="C34" s="0" t="n"/>
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>30913979</t>
+        </is>
+      </c>
       <c r="D34" s="0" t="n"/>
-      <c r="E34" s="0" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="0" t="n"/>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H34" s="0" t="n"/>
-      <c r="I34" s="0" t="n"/>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="n"/>
-      <c r="B35" s="0" t="n"/>
-      <c r="C35" s="0" t="n"/>
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>100560185</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>11106151</t>
+        </is>
+      </c>
       <c r="D35" s="0" t="n"/>
-      <c r="E35" s="0" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="0" t="n"/>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H35" s="0" t="n"/>
-      <c r="I35" s="0" t="n"/>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="n"/>
-      <c r="B36" s="0" t="n"/>
-      <c r="C36" s="0" t="n"/>
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>76940</t>
+        </is>
+      </c>
       <c r="D36" s="0" t="n"/>
-      <c r="E36" s="0" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="0" t="n"/>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H36" s="0" t="n"/>
-      <c r="I36" s="0" t="n"/>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="n"/>
-      <c r="B37" s="0" t="n"/>
-      <c r="C37" s="0" t="n"/>
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>86296</t>
+        </is>
+      </c>
       <c r="D37" s="0" t="n"/>
-      <c r="E37" s="0" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="0" t="n"/>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H37" s="0" t="n"/>
-      <c r="I37" s="0" t="n"/>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="n"/>
-      <c r="B38" s="0" t="n"/>
-      <c r="C38" s="0" t="n"/>
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>210055</t>
+        </is>
+      </c>
       <c r="D38" s="0" t="n"/>
-      <c r="E38" s="0" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="0" t="n"/>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H38" s="0" t="n"/>
-      <c r="I38" s="0" t="n"/>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="n"/>
-      <c r="B39" s="0" t="n"/>
-      <c r="C39" s="0" t="n"/>
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>210056</t>
+        </is>
+      </c>
       <c r="D39" s="0" t="n"/>
-      <c r="E39" s="0" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="0" t="n"/>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H39" s="0" t="n"/>
-      <c r="I39" s="0" t="n"/>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="n"/>
-      <c r="B40" s="0" t="n"/>
-      <c r="C40" s="0" t="n"/>
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>210074</t>
+        </is>
+      </c>
       <c r="D40" s="0" t="n"/>
-      <c r="E40" s="0" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="0" t="n"/>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H40" s="0" t="n"/>
-      <c r="I40" s="0" t="n"/>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="n"/>
-      <c r="B41" s="0" t="n"/>
-      <c r="C41" s="0" t="n"/>
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>210312</t>
+        </is>
+      </c>
       <c r="D41" s="0" t="n"/>
-      <c r="E41" s="0" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="0" t="n"/>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H41" s="0" t="n"/>
-      <c r="I41" s="0" t="n"/>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="n"/>
-      <c r="B42" s="0" t="n"/>
-      <c r="C42" s="0" t="n"/>
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>210313</t>
+        </is>
+      </c>
       <c r="D42" s="0" t="n"/>
-      <c r="E42" s="0" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="0" t="n"/>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H42" s="0" t="n"/>
-      <c r="I42" s="0" t="n"/>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="n"/>
-      <c r="B43" s="0" t="n"/>
-      <c r="C43" s="0" t="n"/>
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>11122106</t>
+        </is>
+      </c>
       <c r="D43" s="0" t="n"/>
-      <c r="E43" s="0" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="0" t="n"/>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H43" s="0" t="n"/>
-      <c r="I43" s="0" t="n"/>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="0" t="n"/>
-      <c r="B44" s="0" t="n"/>
-      <c r="C44" s="0" t="n"/>
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>100560186</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>30300919</t>
+        </is>
+      </c>
       <c r="D44" s="0" t="n"/>
-      <c r="E44" s="0" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="0" t="n"/>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H44" s="0" t="n"/>
-      <c r="I44" s="0" t="n"/>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="0" t="n"/>
-      <c r="B45" s="0" t="n"/>
-      <c r="C45" s="0" t="n"/>
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>72396</t>
+        </is>
+      </c>
       <c r="D45" s="0" t="n"/>
-      <c r="E45" s="0" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="0" t="n"/>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H45" s="0" t="n"/>
-      <c r="I45" s="0" t="n"/>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="0" t="n"/>
-      <c r="B46" s="0" t="n"/>
-      <c r="C46" s="0" t="n"/>
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>72379</t>
+        </is>
+      </c>
       <c r="D46" s="0" t="n"/>
-      <c r="E46" s="0" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="0" t="n"/>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H46" s="0" t="n"/>
-      <c r="I46" s="0" t="n"/>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="0" t="n"/>
-      <c r="B47" s="0" t="n"/>
-      <c r="C47" s="0" t="n"/>
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>11600377</t>
+        </is>
+      </c>
       <c r="D47" s="0" t="n"/>
-      <c r="E47" s="0" t="n"/>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="0" t="n"/>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H47" s="0" t="n"/>
-      <c r="I47" s="0" t="n"/>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="n"/>
-      <c r="B48" s="0" t="n"/>
-      <c r="C48" s="0" t="n"/>
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>30265664</t>
+        </is>
+      </c>
       <c r="D48" s="0" t="n"/>
-      <c r="E48" s="0" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="0" t="n"/>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H48" s="0" t="n"/>
-      <c r="I48" s="0" t="n"/>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="n"/>
-      <c r="B49" s="0" t="n"/>
-      <c r="C49" s="0" t="n"/>
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>11106851</t>
+        </is>
+      </c>
       <c r="D49" s="0" t="n"/>
-      <c r="E49" s="0" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="0" t="n"/>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H49" s="0" t="n"/>
-      <c r="I49" s="0" t="n"/>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="0" t="n"/>
-      <c r="B50" s="0" t="n"/>
-      <c r="C50" s="0" t="n"/>
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>11122756</t>
+        </is>
+      </c>
       <c r="D50" s="0" t="n"/>
-      <c r="E50" s="0" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="0" t="n"/>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H50" s="0" t="n"/>
-      <c r="I50" s="0" t="n"/>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="0" t="n"/>
-      <c r="B51" s="0" t="n"/>
-      <c r="C51" s="0" t="n"/>
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>72406</t>
+        </is>
+      </c>
       <c r="D51" s="0" t="n"/>
-      <c r="E51" s="0" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="0" t="n"/>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H51" s="0" t="n"/>
-      <c r="I51" s="0" t="n"/>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="0" t="n"/>
-      <c r="B52" s="0" t="n"/>
-      <c r="C52" s="0" t="n"/>
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>11122129</t>
+        </is>
+      </c>
       <c r="D52" s="0" t="n"/>
-      <c r="E52" s="0" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="0" t="n"/>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H52" s="0" t="n"/>
-      <c r="I52" s="0" t="n"/>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="0" t="n"/>
-      <c r="B53" s="0" t="n"/>
-      <c r="C53" s="0" t="n"/>
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>100560187</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>50558</t>
+        </is>
+      </c>
       <c r="D53" s="0" t="n"/>
-      <c r="E53" s="0" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="0" t="n"/>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t>CH50</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>Counted, adjusted</t>
+        </is>
+      </c>
       <c r="H53" s="0" t="n"/>
-      <c r="I53" s="0" t="n"/>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="n"/>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -639,8 +639,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>2001</v>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
@@ -676,8 +678,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>2001</v>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
@@ -713,8 +717,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>5001</v>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
@@ -750,8 +756,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>5001</v>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
@@ -787,8 +795,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>5002</v>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
@@ -824,8 +834,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>5003</v>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
@@ -861,8 +873,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>5004</v>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
@@ -898,8 +912,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>5005</v>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
@@ -935,8 +951,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>5006</v>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
@@ -972,8 +990,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>5007</v>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
@@ -1009,8 +1029,10 @@
           <t>CH50</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>3002</v>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
